--- a/data/file_generation/input/data_187/PP01埋点测试最终处理的只保留dataID&eventname_-_副本.xlsx
+++ b/data/file_generation/input/data_187/PP01埋点测试最终处理的只保留dataID&eventname_-_副本.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10913"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\purple\动采\埋点测试结果\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/liyanjie1/Desktop/program/data_clean-20260204/cleaned_data/input/data_187/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{531A37A7-98B0-6643-BA00-8F4CDB85A725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12090"/>
+    <workbookView xWindow="0" yWindow="7860" windowWidth="28800" windowHeight="12100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="46">
   <si>
     <t>vin</t>
   </si>
@@ -90,9 +91,6 @@
     <t>03000102010000000000000000400003</t>
   </si>
   <si>
-    <t>2025-09-19 11:39:18.359</t>
-  </si>
-  <si>
     <t>pcenter</t>
   </si>
   <si>
@@ -105,15 +103,9 @@
     <t>eventname</t>
   </si>
   <si>
-    <t>Hu_Login_Type</t>
-  </si>
-  <si>
     <t>03000102010000000000000000700393</t>
   </si>
   <si>
-    <t>2025-09-19 11:38:04.755</t>
-  </si>
-  <si>
     <t>carset</t>
   </si>
   <si>
@@ -123,68 +115,58 @@
     <t>EventName</t>
   </si>
   <si>
-    <t>hu_CMShighspeedtempviewsetting_BtnClick</t>
-  </si>
-  <si>
     <t>03000102010000000000000000700391</t>
   </si>
   <si>
-    <t>2025-09-19 11:38:03.805</t>
-  </si>
-  <si>
-    <t>hu_CMSturntempviewsetting_BtnClick</t>
-  </si>
-  <si>
     <t>03000102010000000000000000700392</t>
   </si>
   <si>
-    <t>2025-09-19 11:38:02.822</t>
-  </si>
-  <si>
-    <t>hu_CMSreversetempviewsetting_BtnClick</t>
-  </si>
-  <si>
     <t>03000102010000000000000000300131</t>
   </si>
   <si>
-    <t>2025-09-19 11:37:30.334</t>
-  </si>
-  <si>
-    <t>hu_mirrortoast_close</t>
-  </si>
-  <si>
     <t>03000102010000000000000000300127</t>
   </si>
   <si>
-    <t>2025-09-19 11:37:27.653</t>
-  </si>
-  <si>
-    <t>hu_mirrorleftBtn_click</t>
-  </si>
-  <si>
     <t>03000102010000000000000000300128</t>
   </si>
   <si>
-    <t>2025-09-19 11:37:26.855</t>
-  </si>
-  <si>
-    <t>hu_mirrorrightBtn_click</t>
-  </si>
-  <si>
     <t>03000102010000000000000000700388</t>
   </si>
   <si>
-    <t>2025-09-19 11:37:20.936</t>
-  </si>
-  <si>
-    <t>hu_CMSangleadjust_BtnClick</t>
+    <t>-</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20**-**-** **:**:**</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>21**-**-** **:**:**</t>
+  </si>
+  <si>
+    <t>22**-**-** **:**:**</t>
+  </si>
+  <si>
+    <t>23**-**-** **:**:**</t>
+  </si>
+  <si>
+    <t>24**-**-** **:**:**</t>
+  </si>
+  <si>
+    <t>25**-**-** **:**:**</t>
+  </si>
+  <si>
+    <t>26**-**-** **:**:**</t>
+  </si>
+  <si>
+    <t>27**-**-** **:**:**</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -196,6 +178,7 @@
       <b/>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -547,11 +530,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U9"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -616,7 +599,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -633,7 +616,7 @@
         <v>500</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="G2">
         <v>22872370003264</v>
@@ -642,10 +625,10 @@
         <v>21</v>
       </c>
       <c r="I2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" t="s">
         <v>24</v>
-      </c>
-      <c r="J2" t="s">
-        <v>25</v>
       </c>
       <c r="K2">
         <v>65536</v>
@@ -654,39 +637,39 @@
         <v>1</v>
       </c>
       <c r="M2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
+      <c r="O2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T2" t="s">
         <v>26</v>
       </c>
-      <c r="N2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P2" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>26</v>
-      </c>
-      <c r="R2" t="s">
-        <v>26</v>
-      </c>
-      <c r="S2" t="s">
-        <v>26</v>
-      </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
         <v>27</v>
-      </c>
-      <c r="U2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" t="s">
-        <v>29</v>
       </c>
       <c r="C3">
         <v>-1</v>
@@ -698,7 +681,7 @@
         <v>100</v>
       </c>
       <c r="F3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G3">
         <v>22872370003264</v>
@@ -707,10 +690,10 @@
         <v>21</v>
       </c>
       <c r="I3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="K3">
         <v>65536</v>
@@ -719,39 +702,39 @@
         <v>1</v>
       </c>
       <c r="M3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="S3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="U3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:21">
       <c r="A4" t="s">
         <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C4">
         <v>-1</v>
@@ -763,7 +746,7 @@
         <v>100</v>
       </c>
       <c r="F4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G4">
         <v>22872370003264</v>
@@ -772,10 +755,10 @@
         <v>21</v>
       </c>
       <c r="I4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="K4">
         <v>65536</v>
@@ -784,39 +767,39 @@
         <v>1</v>
       </c>
       <c r="M4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="S4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="U4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:21">
       <c r="A5" t="s">
         <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C5">
         <v>-1</v>
@@ -828,7 +811,7 @@
         <v>100</v>
       </c>
       <c r="F5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G5">
         <v>22872370003264</v>
@@ -837,10 +820,10 @@
         <v>21</v>
       </c>
       <c r="I5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="K5">
         <v>65536</v>
@@ -849,39 +832,39 @@
         <v>1</v>
       </c>
       <c r="M5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="S5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T5" t="s">
+        <v>30</v>
+      </c>
+      <c r="U5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
         <v>33</v>
-      </c>
-      <c r="U5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" t="s">
-        <v>41</v>
       </c>
       <c r="C6">
         <v>-1</v>
@@ -902,10 +885,10 @@
         <v>21</v>
       </c>
       <c r="I6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="K6">
         <v>65536</v>
@@ -914,39 +897,39 @@
         <v>1</v>
       </c>
       <c r="M6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N6" t="s">
+        <v>25</v>
+      </c>
+      <c r="O6" t="s">
+        <v>25</v>
+      </c>
+      <c r="P6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>25</v>
+      </c>
+      <c r="R6" t="s">
+        <v>25</v>
+      </c>
+      <c r="S6" t="s">
+        <v>25</v>
+      </c>
+      <c r="T6" t="s">
         <v>26</v>
       </c>
-      <c r="N6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O6" t="s">
-        <v>26</v>
-      </c>
-      <c r="P6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>26</v>
-      </c>
-      <c r="R6" t="s">
-        <v>26</v>
-      </c>
-      <c r="S6" t="s">
-        <v>26</v>
-      </c>
-      <c r="T6" t="s">
-        <v>27</v>
-      </c>
       <c r="U6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:21">
       <c r="A7" t="s">
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C7">
         <v>-1</v>
@@ -958,7 +941,7 @@
         <v>100</v>
       </c>
       <c r="F7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G7">
         <v>22872370003264</v>
@@ -967,10 +950,10 @@
         <v>21</v>
       </c>
       <c r="I7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="K7">
         <v>65536</v>
@@ -979,39 +962,39 @@
         <v>1</v>
       </c>
       <c r="M7" t="s">
+        <v>25</v>
+      </c>
+      <c r="N7" t="s">
+        <v>25</v>
+      </c>
+      <c r="O7" t="s">
+        <v>25</v>
+      </c>
+      <c r="P7" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>25</v>
+      </c>
+      <c r="R7" t="s">
+        <v>25</v>
+      </c>
+      <c r="S7" t="s">
+        <v>25</v>
+      </c>
+      <c r="T7" t="s">
         <v>26</v>
       </c>
-      <c r="N7" t="s">
-        <v>26</v>
-      </c>
-      <c r="O7" t="s">
-        <v>26</v>
-      </c>
-      <c r="P7" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>26</v>
-      </c>
-      <c r="R7" t="s">
-        <v>26</v>
-      </c>
-      <c r="S7" t="s">
-        <v>26</v>
-      </c>
-      <c r="T7" t="s">
-        <v>27</v>
-      </c>
       <c r="U7" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:21">
       <c r="A8" t="s">
         <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C8">
         <v>-1</v>
@@ -1023,7 +1006,7 @@
         <v>100</v>
       </c>
       <c r="F8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G8">
         <v>22872370003264</v>
@@ -1032,10 +1015,10 @@
         <v>21</v>
       </c>
       <c r="I8" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="K8">
         <v>65536</v>
@@ -1044,39 +1027,39 @@
         <v>1</v>
       </c>
       <c r="M8" t="s">
+        <v>25</v>
+      </c>
+      <c r="N8" t="s">
+        <v>25</v>
+      </c>
+      <c r="O8" t="s">
+        <v>25</v>
+      </c>
+      <c r="P8" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>25</v>
+      </c>
+      <c r="R8" t="s">
+        <v>25</v>
+      </c>
+      <c r="S8" t="s">
+        <v>25</v>
+      </c>
+      <c r="T8" t="s">
         <v>26</v>
       </c>
-      <c r="N8" t="s">
-        <v>26</v>
-      </c>
-      <c r="O8" t="s">
-        <v>26</v>
-      </c>
-      <c r="P8" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>26</v>
-      </c>
-      <c r="R8" t="s">
-        <v>26</v>
-      </c>
-      <c r="S8" t="s">
-        <v>26</v>
-      </c>
-      <c r="T8" t="s">
-        <v>27</v>
-      </c>
       <c r="U8" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:21">
       <c r="A9" t="s">
         <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="C9">
         <v>-1</v>
@@ -1088,7 +1071,7 @@
         <v>100</v>
       </c>
       <c r="F9" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G9">
         <v>22872370003264</v>
@@ -1097,10 +1080,10 @@
         <v>21</v>
       </c>
       <c r="I9" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="K9">
         <v>65536</v>
@@ -1109,31 +1092,31 @@
         <v>1</v>
       </c>
       <c r="M9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="S9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T9" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="U9" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1307,13 +1290,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E787AA83-3C25-44A8-8E97-F585A0706FE2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5D8D95F-03A6-4004-9180-40830E14317B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D2CE526A-5D30-4257-9597-4DEC09E53EA9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47EFB2FD-5CCE-4579-A1AE-AB4599B2D393}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{718E8692-34A4-4C3D-88D7-978FD2597C34}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D8E3F8D-FA13-4735-98B6-FA55130B9EB8}"/>
 </file>